--- a/problem 4 part a.xlsx
+++ b/problem 4 part a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Grad School\Spring 2026\Homework 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6102662C-CDE3-446A-A72B-04A3DC7AC2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F43423-015E-458A-9811-C3F6BBCCB18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{C97C3F83-3FE3-4FE4-A50F-AE95D5D46345}"/>
+    <workbookView xWindow="-28920" yWindow="1335" windowWidth="29040" windowHeight="15720" xr2:uid="{C97C3F83-3FE3-4FE4-A50F-AE95D5D46345}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -170,6 +170,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>144555</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>97679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>120170</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>143109</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16F7C79C-C799-FF43-BDD3-0BD3DABB56A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="346261" y="6686738"/>
+          <a:ext cx="5219968" cy="4527783"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -492,12 +541,10 @@
   <dimension ref="A1:AT65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.36328125" customWidth="1"/>
-    <col min="2" max="2" width="2.7265625" customWidth="1"/>
-    <col min="3" max="15" width="2.81640625" customWidth="1"/>
+    <col min="1" max="44" width="2.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:28" ht="26" customHeight="1" x14ac:dyDescent="0.6">
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
@@ -514,7 +561,7 @@
       <c r="N1" s="8"/>
       <c r="O1" s="9"/>
     </row>
-    <row r="2" spans="1:15" ht="26" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:28" ht="26" x14ac:dyDescent="0.6">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -529,7 +576,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -545,8 +592,22 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
@@ -562,8 +623,22 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
       <c r="C5" s="1">
         <v>0</v>
@@ -602,8 +677,45 @@
         <v>11</v>
       </c>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>2</v>
+      </c>
+      <c r="T5" s="1">
+        <v>3</v>
+      </c>
+      <c r="U5" s="1">
+        <v>4</v>
+      </c>
+      <c r="V5" s="1">
+        <v>5</v>
+      </c>
+      <c r="W5" s="1">
+        <v>6</v>
+      </c>
+      <c r="X5" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
@@ -647,8 +759,47 @@
         <v>0</v>
       </c>
       <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="1">
         <v>1</v>
@@ -690,8 +841,47 @@
         <v>0</v>
       </c>
       <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="1">
         <v>2</v>
@@ -733,8 +923,47 @@
         <v>0</v>
       </c>
       <c r="O8" s="7"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="1">
         <v>3</v>
@@ -776,8 +1005,47 @@
         <v>0</v>
       </c>
       <c r="O9" s="7"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="1">
         <v>4</v>
@@ -819,8 +1087,47 @@
         <v>0</v>
       </c>
       <c r="O10" s="7"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="1">
         <v>5</v>
@@ -862,8 +1169,47 @@
         <v>0</v>
       </c>
       <c r="O11" s="7"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="1">
         <v>6</v>
@@ -905,8 +1251,47 @@
         <v>0</v>
       </c>
       <c r="O12" s="7"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>1</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="1">
         <v>7</v>
@@ -948,8 +1333,47 @@
         <v>0</v>
       </c>
       <c r="O13" s="7"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="1">
         <v>8</v>
@@ -991,8 +1415,47 @@
         <v>0</v>
       </c>
       <c r="O14" s="7"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="B15" s="1">
         <v>9</v>
@@ -1034,8 +1497,47 @@
         <v>0</v>
       </c>
       <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2">
+        <v>1</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="B16" s="1">
         <v>10</v>
@@ -1077,8 +1579,47 @@
         <v>0</v>
       </c>
       <c r="O16" s="7"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="B17" s="1">
         <v>11</v>
@@ -1120,8 +1661,47 @@
         <v>1</v>
       </c>
       <c r="O17" s="7"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
@@ -1136,8 +1716,22 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1152,8 +1746,22 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1">
@@ -1192,8 +1800,45 @@
       <c r="N21" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>1</v>
+      </c>
+      <c r="S21" s="1">
+        <v>2</v>
+      </c>
+      <c r="T21" s="1">
+        <v>3</v>
+      </c>
+      <c r="U21" s="1">
+        <v>4</v>
+      </c>
+      <c r="V21" s="1">
+        <v>5</v>
+      </c>
+      <c r="W21" s="1">
+        <v>6</v>
+      </c>
+      <c r="X21" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1881,47 @@
       <c r="N22" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="1">
         <v>1</v>
@@ -1278,8 +1962,47 @@
       <c r="N23" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>1</v>
+      </c>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="1">
         <v>2</v>
@@ -1320,8 +2043,47 @@
       <c r="N24" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P24" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>1</v>
+      </c>
+      <c r="T24" s="2">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" s="6"/>
       <c r="B25" s="1">
         <v>3</v>
@@ -1362,8 +2124,47 @@
       <c r="N25" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P25" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <v>1</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="1">
         <v>4</v>
@@ -1404,8 +2205,47 @@
       <c r="N26" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P26" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2">
+        <v>1</v>
+      </c>
+      <c r="W26" s="2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
       <c r="B27" s="1">
         <v>5</v>
@@ -1446,8 +2286,47 @@
       <c r="N27" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P27" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2">
+        <v>1</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
       <c r="B28" s="1">
         <v>6</v>
@@ -1488,8 +2367,47 @@
       <c r="N28" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P28" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2">
+        <v>0</v>
+      </c>
+      <c r="X28" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
       <c r="B29" s="1">
         <v>7</v>
@@ -1530,8 +2448,47 @@
       <c r="N29" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P29" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2">
+        <v>0</v>
+      </c>
+      <c r="X29" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
       <c r="B30" s="1">
         <v>8</v>
@@ -1572,8 +2529,47 @@
       <c r="N30" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P30" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>1</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2">
+        <v>0</v>
+      </c>
+      <c r="X30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
       <c r="B31" s="1">
         <v>9</v>
@@ -1614,8 +2610,47 @@
       <c r="N31" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P31" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2">
+        <v>0</v>
+      </c>
+      <c r="X31" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
       <c r="B32" s="1">
         <v>10</v>
@@ -1656,8 +2691,47 @@
       <c r="N32" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="P32" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2">
+        <v>0</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
       <c r="B33" s="1">
         <v>11</v>
@@ -1698,1170 +2772,135 @@
       <c r="N33" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C36" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="P33" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2">
+        <v>0</v>
+      </c>
+      <c r="W33" s="2">
+        <v>0</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1">
-        <v>0</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1">
-        <v>3</v>
-      </c>
-      <c r="G37" s="1">
-        <v>4</v>
-      </c>
-      <c r="H37" s="1">
-        <v>5</v>
-      </c>
-      <c r="I37" s="1">
-        <v>6</v>
-      </c>
-      <c r="J37" s="1">
-        <v>7</v>
-      </c>
-      <c r="K37" s="1">
-        <v>8</v>
-      </c>
-      <c r="L37" s="1">
-        <v>9</v>
-      </c>
-      <c r="M37" s="1">
-        <v>10</v>
-      </c>
-      <c r="N37" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="1">
-        <v>0</v>
-      </c>
-      <c r="C38" s="2">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2">
-        <v>1</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
-      <c r="B40" s="1">
-        <v>2</v>
-      </c>
-      <c r="C40" s="2">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
-      <c r="B41" s="1">
-        <v>3</v>
-      </c>
-      <c r="C41" s="2">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2">
-        <v>0</v>
-      </c>
-      <c r="K41" s="2">
-        <v>0</v>
-      </c>
-      <c r="L41" s="2">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
-      <c r="B42" s="1">
-        <v>4</v>
-      </c>
-      <c r="C42" s="2">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
-      <c r="B43" s="1">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
-      <c r="B44" s="1">
-        <v>6</v>
-      </c>
-      <c r="C44" s="2">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
-      <c r="B45" s="1">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2">
-        <v>0</v>
-      </c>
-      <c r="M45" s="2">
-        <v>1</v>
-      </c>
-      <c r="N45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
-      <c r="B46" s="1">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2">
-        <v>0</v>
-      </c>
-      <c r="M46" s="2">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A47" s="6"/>
-      <c r="B47" s="1">
-        <v>9</v>
-      </c>
-      <c r="C47" s="2">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2">
-        <v>0</v>
-      </c>
-      <c r="K47" s="2">
-        <v>0</v>
-      </c>
-      <c r="L47" s="2">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0</v>
-      </c>
-      <c r="N47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A48" s="6"/>
-      <c r="B48" s="1">
-        <v>10</v>
-      </c>
-      <c r="C48" s="2">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2">
-        <v>0</v>
-      </c>
-      <c r="M48" s="2">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
-      <c r="B49" s="1">
-        <v>11</v>
-      </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2">
-        <v>1</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2">
-        <v>0</v>
-      </c>
-      <c r="M49" s="2">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C51" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1">
-        <v>0</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="1">
-        <v>2</v>
-      </c>
-      <c r="F53" s="1">
-        <v>3</v>
-      </c>
-      <c r="G53" s="1">
-        <v>4</v>
-      </c>
-      <c r="H53" s="1">
-        <v>5</v>
-      </c>
-      <c r="I53" s="1">
-        <v>6</v>
-      </c>
-      <c r="J53" s="1">
-        <v>7</v>
-      </c>
-      <c r="K53" s="1">
-        <v>8</v>
-      </c>
-      <c r="L53" s="1">
-        <v>9</v>
-      </c>
-      <c r="M53" s="1">
-        <v>10</v>
-      </c>
-      <c r="N53" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="1">
-        <v>0</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1</v>
-      </c>
-      <c r="D54" s="2">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2">
-        <v>0</v>
-      </c>
-      <c r="N54" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
-      <c r="B55" s="1">
-        <v>1</v>
-      </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
-      <c r="K55" s="2">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2">
-        <v>0</v>
-      </c>
-      <c r="M55" s="2">
-        <v>0</v>
-      </c>
-      <c r="N55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
-      <c r="B56" s="1">
-        <v>2</v>
-      </c>
-      <c r="C56" s="2">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2">
-        <v>0</v>
-      </c>
-      <c r="L56" s="2">
-        <v>0</v>
-      </c>
-      <c r="M56" s="2">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
-      <c r="B57" s="1">
-        <v>3</v>
-      </c>
-      <c r="C57" s="2">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
-      <c r="B58" s="1">
-        <v>4</v>
-      </c>
-      <c r="C58" s="2">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2">
-        <v>1</v>
-      </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
-      <c r="K58" s="2">
-        <v>0</v>
-      </c>
-      <c r="L58" s="2">
-        <v>0</v>
-      </c>
-      <c r="M58" s="2">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
-      <c r="B59" s="1">
-        <v>5</v>
-      </c>
-      <c r="C59" s="2">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0</v>
-      </c>
-      <c r="K59" s="2">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>0</v>
-      </c>
-      <c r="M59" s="2">
-        <v>0</v>
-      </c>
-      <c r="N59" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="6"/>
-      <c r="B60" s="1">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
-        <v>1</v>
-      </c>
-      <c r="K60" s="2">
-        <v>0</v>
-      </c>
-      <c r="L60" s="2">
-        <v>0</v>
-      </c>
-      <c r="M60" s="2">
-        <v>0</v>
-      </c>
-      <c r="N60" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
-      <c r="B61" s="1">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>0</v>
-      </c>
-      <c r="G61" s="2">
-        <v>0</v>
-      </c>
-      <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>1</v>
-      </c>
-      <c r="K61" s="2">
-        <v>0</v>
-      </c>
-      <c r="L61" s="2">
-        <v>0</v>
-      </c>
-      <c r="M61" s="2">
-        <v>0</v>
-      </c>
-      <c r="N61" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
-      <c r="B62" s="1">
-        <v>8</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1</v>
-      </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2">
-        <v>0</v>
-      </c>
-      <c r="F62" s="2">
-        <v>0</v>
-      </c>
-      <c r="G62" s="2">
-        <v>0</v>
-      </c>
-      <c r="H62" s="2">
-        <v>0</v>
-      </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
-        <v>0</v>
-      </c>
-      <c r="K62" s="2">
-        <v>0</v>
-      </c>
-      <c r="L62" s="2">
-        <v>0</v>
-      </c>
-      <c r="M62" s="2">
-        <v>0</v>
-      </c>
-      <c r="N62" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
-      <c r="B63" s="1">
-        <v>9</v>
-      </c>
-      <c r="C63" s="2">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2">
-        <v>0</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0</v>
-      </c>
-      <c r="G63" s="2">
-        <v>0</v>
-      </c>
-      <c r="H63" s="2">
-        <v>0</v>
-      </c>
-      <c r="I63" s="2">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2">
-        <v>1</v>
-      </c>
-      <c r="K63" s="2">
-        <v>0</v>
-      </c>
-      <c r="L63" s="2">
-        <v>0</v>
-      </c>
-      <c r="M63" s="2">
-        <v>0</v>
-      </c>
-      <c r="N63" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
-      <c r="B64" s="1">
-        <v>10</v>
-      </c>
-      <c r="C64" s="2">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2">
-        <v>0</v>
-      </c>
-      <c r="F64" s="2">
-        <v>0</v>
-      </c>
-      <c r="G64" s="2">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2">
-        <v>0</v>
-      </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2">
-        <v>0</v>
-      </c>
-      <c r="K64" s="2">
-        <v>0</v>
-      </c>
-      <c r="L64" s="2">
-        <v>0</v>
-      </c>
-      <c r="M64" s="2">
-        <v>1</v>
-      </c>
-      <c r="N64" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="6"/>
-      <c r="B65" s="1">
-        <v>11</v>
-      </c>
-      <c r="C65" s="2">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2">
-        <v>0</v>
-      </c>
-      <c r="E65" s="2">
-        <v>0</v>
-      </c>
-      <c r="F65" s="2">
-        <v>0</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0</v>
-      </c>
-      <c r="H65" s="2">
-        <v>0</v>
-      </c>
-      <c r="I65" s="2">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2">
-        <v>0</v>
-      </c>
-      <c r="K65" s="2">
-        <v>0</v>
-      </c>
-      <c r="L65" s="2">
-        <v>0</v>
-      </c>
-      <c r="M65" s="2">
-        <v>0</v>
-      </c>
-      <c r="N65" s="2">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C35:N35"/>
-    <mergeCell ref="C36:N36"/>
+    <mergeCell ref="Q3:AB3"/>
+    <mergeCell ref="Q4:AB4"/>
     <mergeCell ref="A38:A49"/>
-    <mergeCell ref="C51:N51"/>
-    <mergeCell ref="C52:N52"/>
+    <mergeCell ref="Q19:AB19"/>
+    <mergeCell ref="Q20:AB20"/>
     <mergeCell ref="A54:A65"/>
     <mergeCell ref="C19:N19"/>
     <mergeCell ref="C20:N20"/>
@@ -2872,5 +2911,6 @@
     <mergeCell ref="C3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>